--- a/course/spec/Course_Specification_ITCS355_merged.xlsx
+++ b/course/spec/Course_Specification_ITCS355_merged.xlsx
@@ -1460,12 +1460,12 @@
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>INTERNAL CONFLICT IN THE OFFICIAL FILE. Column G (WEIGHT) is 3 for all five criteria, so SCORE = MAX LEVEL 3 x WEIGHT 3 = 9 each and the sheet totals 45. The same workbook's 'Evaluation Method' prices 'Capstone System' at 30. Set WEIGHT to 2, which makes each criterion 6 and the sheet total exactly 30.</t>
+          <t>INTERNAL CONFLICT IN THE OFFICIAL FILE. Column G (WEIGHT) is 3 for all five criteria, so SCORE = MAX LEVEL 3 x WEIGHT 3 = 9 each and the sheet totals 45. The same workbook's 'Evaluation Method' prices 'Capstone System' at 30, and the file gives no conversion between the two. WEIGHT is set to 2 here, which makes each criterion 6 and the sheet total exactly 30.</t>
         </is>
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>CONFIRM. The alternative is to keep weight 3 and reprice 'Capstone System' to 45, which then breaks the 100-mark total.</t>
+          <t>DECIDED — weight 2, approved by Dr. Pasd Putthapipat on 4 September 2026. The alternatives were rejected: repricing 'Capstone System' to 45 pushes the course total to 115, and marking out of 45 then scaling by 30/45 shows students two different numbers and creates fractional marks on appeal. Still to do: tell the faculty, because the file held in the university system continues to compute 45. Re-apply this edit after any re-issue.</t>
         </is>
       </c>
     </row>

--- a/course/spec/Course_Specification_ITCS355_merged.xlsx
+++ b/course/spec/Course_Specification_ITCS355_merged.xlsx
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>The Lab 3 service migrated onto a managed cloud platform, with IAM roles and a cost report</t>
+          <t>The Lab 3 service migrated onto a managed cloud platform with IAM roles and a cost report, plus an LLM step with a golden-set eval gate and a token bill</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>The service runs on managed infrastructure, resources are torn down, and the cost figure matches billing within 20%</t>
+          <t>The service runs on managed infrastructure, resources are torn down, the cost figure matches billing within 20%, and the eval gate demonstrably fails on a degraded response set</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
@@ -1074,7 +1074,7 @@
       <c r="D8" s="17" t="inlineStr"/>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr"/>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>AUTHOR THE LLM CONTENT before Session 5 runs, or ask the faculty to restore the previous 'Cloud MLOps' title.</t>
+          <t>PARTLY DONE, 4 September 2026. Lab 5 Part B now covers the LLM-operations half: evaluation gate, guardrails, token accounting. Remaining: Session 5 slides for that half and Drill 5 questions on it. Note the workload consequence — Lab 5 goes from 5 to 7 self-study hours and the term total from 40 to 42 against a nominal 30. Decide whether to absorb it or trim Part A.</t>
         </is>
       </c>
     </row>
@@ -3173,12 +3173,12 @@
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>Lab 5 — Cloud migration + cost report</t>
+          <t>Lab 5 — Cloud migration + cost report + LLM eval gate</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">
@@ -3200,7 +3200,7 @@
       <c r="F8" s="17" t="inlineStr"/>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H8" s="17" t="n"/>
@@ -3218,7 +3218,7 @@
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>Workload note: the 1(1-0-2) credit structure allocates a nominal 30 self-study hours over the term. The plan above totals 40 (23 hours of labs plus 17 of project work). Options to close the gap: drop Lab 5 and fold the cloud migration into the capstone (-5), and trim capstone scope (-5). A modest overrun is normal for a project-based course, but it should be a deliberate choice rather than an accident.</t>
+          <t>Workload note: the 1(1-0-2) credit structure allocates a nominal 30 self-study hours over the term. The plan above totals 42 (25 hours of labs plus 17 of capstone work), up from 40 when Lab 5 Part B was added. Options to close the gap: fold Lab 5 Part A's cloud migration into the capstone (-5), and trim capstone scope (-5). A modest overrun is normal for a project-based course, but it should be a deliberate choice rather than an accident.</t>
         </is>
       </c>
       <c r="B10" s="17" t="n"/>
@@ -3242,7 +3242,7 @@
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>CONTENT GAP — Session 5. The official topic is 'Operating LLM systems and defending the bill'. The cost and FinOps half is fully written (Lab 5, scripts/cost_report.py). The LLM-operations half is currently one subtopic line and has no lab exercise, no slide detail, and no drill questions behind it. It needs authoring before the session runs.</t>
+          <t>Session 5, LLM half — FIRST INCREMENT WRITTEN. Lab 5 Part B (Tasks 7 to 9) covers the evaluation gate, guardrails, and token cost, backed by src/llmcost.py, scripts/llm_eval.py, a worked golden set under evals/, and tests. STILL TO WRITE: the Session 5 slide deck for this half, Drill 5 questions on it, and a live managed-LLM-endpoint walkthrough — the lab runs on recorded responses so it stays free and offline.</t>
         </is>
       </c>
       <c r="B12" s="17" t="n"/>

--- a/course/spec/Course_Specification_ITCS355_merged.xlsx
+++ b/course/spec/Course_Specification_ITCS355_merged.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>PARTLY DONE, 4 September 2026. Lab 5 Part B now covers the LLM-operations half: evaluation gate, guardrails, token accounting. Remaining: Session 5 slides for that half and Drill 5 questions on it. Note the workload consequence — Lab 5 goes from 5 to 7 self-study hours and the term total from 40 to 42 against a nominal 30. Decide whether to absorb it or trim Part A.</t>
+          <t>DONE, 4 September 2026, except one item. The LLM-operations half of Session 5 now has lab tasks, code, tests, slides in both decks, and a drill paper. Outstanding: a live managed-endpoint walkthrough for the room. Note the workload consequence — Lab 5 went from 5 to 7 self-study hours and the term total from 40 to 42 against a nominal 30. Decide whether to absorb it or trim Part A.</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>Session 5, LLM half — FIRST INCREMENT WRITTEN. Lab 5 Part B (Tasks 7 to 9) covers the evaluation gate, guardrails, and token cost, backed by src/llmcost.py, scripts/llm_eval.py, a worked golden set under evals/, and tests. STILL TO WRITE: the Session 5 slide deck for this half, Drill 5 questions on it, and a live managed-LLM-endpoint walkthrough — the lab runs on recorded responses so it stays free and offline.</t>
+          <t>Session 5, LLM half — WRITTEN. Lab 5 Part B (Tasks 7 to 9) covers the evaluation gate, guardrails and token cost, backed by src/llmcost.py, scripts/llm_eval.py, a worked golden set under evals/ and tests; three slides in both decks; and the drill paper at instructor/drills/drill-05.md. STILL TO DO: a live managed-LLM-endpoint walkthrough for the room — the lab deliberately runs on recorded responses so it stays free, offline and identical for every student.</t>
         </is>
       </c>
       <c r="B12" s="17" t="n"/>
